--- a/output_data/AC_PV_OG.xlsx
+++ b/output_data/AC_PV_OG.xlsx
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.27649344260552</v>
+        <v>45.9256985230156</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>324.6942852457739</v>
+        <v>336.7884558354478</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>501.8002590161959</v>
+        <v>520.4912499275102</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>654.3081808740595</v>
+        <v>678.6797670623419</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>870.7710377045753</v>
+        <v>903.2054042859736</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>873.2308428958312</v>
+        <v>905.7568319816968</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>902.7485051909016</v>
+        <v>936.3739643303738</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>892.9092844258781</v>
+        <v>926.1682535474815</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>912.5877259559251</v>
+        <v>946.5796751132663</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>730.5621418029912</v>
+        <v>757.7740256297576</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>573.134609562616</v>
+        <v>594.4826531034799</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>415.7070773222408</v>
+        <v>431.1912805772022</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>268.118765846889</v>
+        <v>278.1056188338168</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.7137661201876</v>
+        <v>81.64568626313887</v>
       </c>
     </row>
     <row r="21">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2459.805191255863</v>
+        <v>2551.42769572309</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/AC_PV_OG.xlsx
+++ b/output_data/AC_PV_OG.xlsx
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.9256985230156</v>
+        <v>46.4836142629582</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>336.7884558354478</v>
+        <v>340.8798379283601</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>520.4912499275102</v>
+        <v>526.8142949801929</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>678.6797670623419</v>
+        <v>686.9245218859379</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>903.2054042859736</v>
+        <v>914.1777471715112</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>905.7568319816968</v>
+        <v>916.76017018612</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>936.3739643303738</v>
+        <v>947.7492463614255</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>926.1682535474815</v>
+        <v>937.4195543029904</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>946.5796751132663</v>
+        <v>958.0789384198607</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>757.7740256297576</v>
+        <v>766.9796353388102</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>594.4826531034799</v>
+        <v>601.7045624038478</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>431.1912805772022</v>
+        <v>436.4294894688854</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>278.1056188338168</v>
+        <v>281.484108592358</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>81.64568626313887</v>
+        <v>82.63753646748124</v>
       </c>
     </row>
     <row r="21">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2551.42769572309</v>
+        <v>2582.423014608789</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/AC_PV_OG.xlsx
+++ b/output_data/AC_PV_OG.xlsx
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.4836142629582</v>
+        <v>44.26311955918198</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>340.8798379283601</v>
+        <v>324.5962101006679</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>526.8142949801929</v>
+        <v>501.6486883373958</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>686.9245218859379</v>
+        <v>654.1105445968005</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>914.1777471715112</v>
+        <v>870.5080179972457</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>916.76017018612</v>
+        <v>872.9670801949781</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>947.7492463614255</v>
+        <v>902.475826567766</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>937.4195543029904</v>
+        <v>892.6395777768367</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>958.0789384198607</v>
+        <v>912.3120753586954</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>766.9796353388102</v>
+        <v>730.3414727265027</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>601.7045624038478</v>
+        <v>572.9614920716335</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>436.4294894688854</v>
+        <v>415.5815114167642</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>281.484108592358</v>
+        <v>268.0377795528242</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>82.63753646748124</v>
+        <v>78.68999032743464</v>
       </c>
     </row>
     <row r="21">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2582.423014608789</v>
+        <v>2459.062197732333</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/AC_PV_OG.xlsx
+++ b/output_data/AC_PV_OG.xlsx
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.26311955918198</v>
+        <v>46.86693679189776</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>324.5962101006679</v>
+        <v>343.6908698072503</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>501.6486883373958</v>
+        <v>531.1586169748413</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>654.1105445968005</v>
+        <v>692.5891770358226</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>870.5080179972457</v>
+        <v>921.7164235739892</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>872.9670801949781</v>
+        <v>924.3201422846503</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>902.475826567766</v>
+        <v>955.5647668125821</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>892.6395777768367</v>
+        <v>945.1498919699382</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>912.3120753586954</v>
+        <v>965.979641655226</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>730.3414727265027</v>
+        <v>773.304457066313</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>572.9614920716335</v>
+        <v>606.66645958401</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>415.5815114167642</v>
+        <v>440.0284621017068</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>268.0377795528242</v>
+        <v>283.8053394620475</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.68999032743464</v>
+        <v>83.31899874115157</v>
       </c>
     </row>
     <row r="21">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2459.062197732333</v>
+        <v>2603.718710660987</v>
       </c>
     </row>
   </sheetData>
